--- a/data/trending_integrated_20260908_11.xlsx
+++ b/data/trending_integrated_20260908_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>140894492463</v>
+        <v>141041748663</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 및 6G 광통신 부품 국산화 사업 선정. 정부 주관 사업 참여 관련 기대감.</t>
+          <t>AI 데이터센터 관련 정부 주관 사업 선정 및 국산화 수행 기관 지정 사실이 부각됨. 광통신 사업과의 연관성을 언급하며 주가 상승 가능성을 제기함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '6G', '광통신']</t>
+          <t>['AI 데이터센터', '광통신', '정부 사업']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10500</v>
+        <v>10410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+24.70%</t>
+          <t>+23.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>249629237955</v>
+        <v>253071240960</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 구체화 및 전략적 투자 관련 논의. 긍정적 기대감과 함께 일부 부정적 전망도 존재.</t>
+          <t>정부의 미프진 도입 구체화 및 연내 허가 관련 뉴스가 언급되며 주가 상승 기대감이 형성됨. 다만, 관련 뉴스 인용 외 구체적인 실적 근거는 부족함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 정책', '낙태약']</t>
+          <t>['미프진', '정부 도입', '연내 허가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36700</v>
+        <v>37100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+20.13%</t>
+          <t>+21.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F4" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G4" t="n">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>699629355875</v>
+        <v>707071245950</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 세계 최초 비대면 진료 플랫폼 개발 관련 논의. 11시 급등 기대감.</t>
+          <t>세계 최초 반지형 웨어러블 디바이스 관련 기술력과 정부 지분 공시 등 긍정적 요인이 부각되며 급등 기대감이 형성됨. 주포 개입 가능성을 언급하며 강한 상승세를 예상함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비대면 진료', '정부 지분', '플랫폼']</t>
+          <t>['웨어러블 디바이스', '정부 지분', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4070</v>
+        <v>139200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.69%</t>
+          <t>+13.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="H5" t="n">
-        <v>1.56</v>
+        <v>13.33</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3580</v>
+        <v>122300</v>
       </c>
       <c r="K5" t="n">
-        <v>3600</v>
+        <v>129400</v>
       </c>
       <c r="L5" t="n">
-        <v>4335</v>
+        <v>143100</v>
       </c>
       <c r="M5" t="n">
-        <v>3450</v>
+        <v>128100</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>213803012109</v>
+        <v>146761411400</v>
       </c>
       <c r="P5" t="n">
-        <v>4335</v>
+        <v>198000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1246</v>
+        <v>77100</v>
       </c>
       <c r="R5" t="n">
-        <v>-338000</v>
+        <v>-11000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 기대감과 함께 건보료 적용 가능성 논의. 목표가 30만 원 제시.</t>
+          <t>미국 원전 8기 수주 관련 260조 사업 규모의 구체적인 내용과 수익 계산법이 제시되며 긍정적인 전망이 우세함. 기관 및 연기금의 순매수세 유입도 긍정적 신호로 작용함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료', '신약']</t>
+          <t>['원전 사업', '260조', '기관 연기금']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>052690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138300</v>
+        <v>4070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.08%</t>
+          <t>+13.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="H6" t="n">
-        <v>13.33</v>
+        <v>1.56</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>122300</v>
+        <v>3580</v>
       </c>
       <c r="K6" t="n">
-        <v>129400</v>
+        <v>3600</v>
       </c>
       <c r="L6" t="n">
-        <v>143100</v>
+        <v>4335</v>
       </c>
       <c r="M6" t="n">
-        <v>128100</v>
+        <v>3450</v>
       </c>
       <c r="N6" t="n">
-        <v>13.22</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>143420195500</v>
+        <v>220133090515</v>
       </c>
       <c r="P6" t="n">
-        <v>198000</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>77100</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>-338000</v>
       </c>
       <c r="S6" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 및 260조 사업 관련 논의. 웨스팅 지분 급물살 및 신사업 진출 기대.</t>
+          <t>탈모 치료제 관련 건보료 적용 기대감으로 긍정적인 논조가 형성됨. 다만, 구체적인 실적 발표나 공시보다는 기대감에 기반한 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '미국 수주', '260조 사업']</t>
+          <t>['탈모 치료제', '건보료 적용', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.17%</t>
+          <t>+11.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="H7" t="n">
         <v>10.47</v>
@@ -1070,7 +1070,7 @@
         <v>10.4</v>
       </c>
       <c r="O7" t="n">
-        <v>303977118915</v>
+        <v>311660409665</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 건설 수주 및 에너지 인프라 사업 확대 기대감. 2만 원 돌파 및 시총 저평가 논의.</t>
+          <t>원전 사업 수주 및 미국 원전 건설 관련 뉴스가 부각되며 주가 상승 기대감이 높음. 2만 돌파 및 시가총액 저평가 의견이 제시되며 긍정적인 전망을 보임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '에너지 인프라', '수주']</t>
+          <t>['원전', '신사업', '미국 건설']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11830</v>
+        <v>11990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.33%</t>
+          <t>+9.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
         <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H8" t="n">
         <v>5.42</v>
@@ -1162,7 +1162,7 @@
         <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>99115349020</v>
+        <v>101739671470</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 소식. 15000원 목표가 제시.</t>
+          <t>프랑스와의 원자력 협정 체결 및 미국 원전 8기 수주 관련 뉴스가 주가 상승 모멘텀으로 작용하고 있음. 원전 섹터 전반의 강세와 함께 긍정적 전망을 보임.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '원자력 협정', '공매도']</t>
+          <t>['원자력 협정', '미국 원전', '원전 섹터']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+7.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
         <v>5.34</v>
@@ -1254,7 +1254,7 @@
         <v>5.29</v>
       </c>
       <c r="O9" t="n">
-        <v>7094841844</v>
+        <v>7191481676</v>
       </c>
       <c r="P9" t="n">
         <v>901</v>
@@ -1299,276 +1299,276 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50700</v>
+        <v>14150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>188</v>
+        <v>425</v>
       </c>
       <c r="H10" t="n">
-        <v>38.34</v>
+        <v>1.94</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>48000</v>
+        <v>13470</v>
       </c>
       <c r="K10" t="n">
-        <v>48550</v>
+        <v>13580</v>
       </c>
       <c r="L10" t="n">
-        <v>51600</v>
+        <v>14450</v>
       </c>
       <c r="M10" t="n">
-        <v>48350</v>
+        <v>13420</v>
       </c>
       <c r="N10" t="n">
-        <v>38.24</v>
+        <v>1.82</v>
       </c>
       <c r="O10" t="n">
-        <v>98039533975</v>
+        <v>178608753115</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>-161000</v>
       </c>
       <c r="S10" t="n">
-        <v>66000</v>
+        <v>11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['광통신', 'Texas', '투경']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14210</v>
+        <v>50400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.49%</t>
+          <t>+5.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>404</v>
+        <v>188</v>
       </c>
       <c r="H11" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K11" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L11" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M11" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O11" t="n">
-        <v>176522062170</v>
+        <v>100309016575</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>-161000</v>
+        <v>275000</v>
       </c>
       <c r="S11" t="n">
-        <v>11000</v>
+        <v>66000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 광통신 사업 관련 논의. 투기과열종목 지정 여부 판단 시점.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'Texas', '투기과열']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15250</v>
+        <v>92000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.10%</t>
+          <t>+4.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>364</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="G12" t="n">
-        <v>46</v>
+        <v>1701</v>
       </c>
       <c r="H12" t="n">
-        <v>1.72</v>
+        <v>23.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14650</v>
+        <v>87900</v>
       </c>
       <c r="K12" t="n">
-        <v>15100</v>
+        <v>91200</v>
       </c>
       <c r="L12" t="n">
-        <v>16680</v>
+        <v>93500</v>
       </c>
       <c r="M12" t="n">
-        <v>14800</v>
+        <v>90200</v>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>23.53</v>
       </c>
       <c r="O12" t="n">
-        <v>43604548790</v>
+        <v>301042717300</v>
       </c>
       <c r="P12" t="n">
-        <v>21400</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>12090</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-3000</v>
+        <v>-222000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>267000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1579,27 +1579,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34050</v>
+        <v>34250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.97%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="H13" t="n">
-        <v>52.68</v>
+        <v>52.69</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>52633435675</v>
+        <v>55203062750</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91300</v>
+        <v>1850000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+3.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>361</v>
+        <v>797</v>
       </c>
       <c r="F14" t="n">
-        <v>227</v>
+        <v>469</v>
       </c>
       <c r="G14" t="n">
-        <v>1722</v>
+        <v>2128</v>
       </c>
       <c r="H14" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>87900</v>
+        <v>1783000</v>
       </c>
       <c r="K14" t="n">
-        <v>91200</v>
+        <v>1799000</v>
       </c>
       <c r="L14" t="n">
-        <v>93500</v>
+        <v>1860000</v>
       </c>
       <c r="M14" t="n">
-        <v>90200</v>
+        <v>1777000</v>
       </c>
       <c r="N14" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>291287379200</v>
+        <v>3041898609500</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R14" t="n">
-        <v>-222000</v>
+        <v>-8000</v>
       </c>
       <c r="S14" t="n">
-        <v>267000</v>
+        <v>108000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>낸드메모리 품귀 현상 및 반도체 시즌 2 도래 전망으로 주가 상승 기대감이 높음. 기관 및 외인 매수세 유입과 함께 300만 돌파 목표를 제시하는 등 긍정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['낸드메모리', '반도체', '기관 외인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9120</v>
+        <v>15140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8780</v>
+        <v>14650</v>
       </c>
       <c r="K15" t="n">
-        <v>9060</v>
+        <v>15100</v>
       </c>
       <c r="L15" t="n">
-        <v>9960</v>
+        <v>16680</v>
       </c>
       <c r="M15" t="n">
-        <v>8270</v>
+        <v>14800</v>
       </c>
       <c r="N15" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>96313536550</v>
+        <v>43952456650</v>
       </c>
       <c r="P15" t="n">
-        <v>25050</v>
+        <v>21400</v>
       </c>
       <c r="Q15" t="n">
-        <v>3705</v>
+        <v>12090</v>
       </c>
       <c r="R15" t="n">
-        <v>-59000</v>
+        <v>-3000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1851500</v>
+        <v>276750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+3.84%</t>
+          <t>+2.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F16" t="n">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="G16" t="n">
-        <v>2187</v>
+        <v>1740</v>
       </c>
       <c r="H16" t="n">
-        <v>50.63</v>
+        <v>46.79</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1783000</v>
+        <v>270000</v>
       </c>
       <c r="K16" t="n">
-        <v>1799000</v>
+        <v>272000</v>
       </c>
       <c r="L16" t="n">
-        <v>1860000</v>
+        <v>277500</v>
       </c>
       <c r="M16" t="n">
-        <v>1777000</v>
+        <v>269000</v>
       </c>
       <c r="N16" t="n">
-        <v>50.5</v>
+        <v>46.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2928879682000</v>
+        <v>2240704915000</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>274000</v>
+        <v>69600</v>
       </c>
       <c r="R16" t="n">
-        <v>-8000</v>
+        <v>1295000</v>
       </c>
       <c r="S16" t="n">
-        <v>108000</v>
+        <v>223000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>메모리 반도체 품귀 현상 및 재고 감소 추세. 300만 원 돌파 목표 및 기관/외인 매수세 유입 기대.</t>
+          <t>15조 규모 자사주 매수 및 주주환원 정책 발표로 긍정적 투자 심리가 형성됨. 30만 전자 목표 언급과 함께 개인 투자자들의 홀딩 의견이 지배적이나, 정치적 언급이 다소 혼재됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체', '메모리', '재고']</t>
+          <t>['자사주 매수', '주주환원', '반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,99 +1936,99 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>276500</v>
+        <v>8960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.41%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>796</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>466</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>1659</v>
+        <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>46.79</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>270000</v>
+        <v>8780</v>
       </c>
       <c r="K17" t="n">
-        <v>272000</v>
+        <v>9060</v>
       </c>
       <c r="L17" t="n">
-        <v>277500</v>
+        <v>9960</v>
       </c>
       <c r="M17" t="n">
-        <v>269000</v>
+        <v>8270</v>
       </c>
       <c r="N17" t="n">
-        <v>46.73</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>2082423099250</v>
+        <v>98256381975</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>25050</v>
       </c>
       <c r="Q17" t="n">
-        <v>69600</v>
+        <v>3705</v>
       </c>
       <c r="R17" t="n">
-        <v>1295000</v>
+        <v>-59000</v>
       </c>
       <c r="S17" t="n">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 발표 및 주주환원 정책 기대감. 반도체 사업 및 로봇 출시 관련 논의.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['자사주 매수', '주주환원', '반도체']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10260</v>
+        <v>10240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>56403892280</v>
+        <v>56786381370</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15490</v>
+        <v>15520</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>29224130810</v>
+        <v>29661605860</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12120</v>
+        <v>11970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-5.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>23389261050</v>
+        <v>24190282355</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8400</v>
+        <v>8340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.21%</t>
+          <t>-11.84%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>23893961760</v>
+        <v>24813441985</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>

--- a/data/trending_integrated_20260908_11.xlsx
+++ b/data/trending_integrated_20260908_11.xlsx
@@ -578,10 +578,10 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>151</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141041748663</v>
+        <v>141314522983</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 관련 정부 주관 사업 선정 및 국산화 수행 기관 지정 사실이 부각됨. 광통신 사업과의 연관성을 언급하며 주가 상승 가능성을 제기함.</t>
+          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 상용화 관련 재료 부각. 최소 3방 이상 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '정부 사업']</t>
+          <t>['AI 데이터센터', '국산화', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10410</v>
+        <v>10360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.63%</t>
+          <t>+23.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>253071240960</v>
+        <v>259954044870</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 미프진 도입 구체화 및 연내 허가 관련 뉴스가 언급되며 주가 상승 기대감이 형성됨. 다만, 관련 뉴스 인용 외 구체적인 실적 근거는 부족함.</t>
+          <t>정부의 미프진 도입 구체화 및 연내 허가 뉴스 기반 주가 상승 기대감. 그러나 원내/약국 처방 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '정부 도입', '연내 허가']</t>
+          <t>['미프진', '정부 도입', '낙태약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37100</v>
+        <v>37200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.44%</t>
+          <t>+21.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="F4" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G4" t="n">
-        <v>825</v>
+        <v>899</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>707071245950</v>
+        <v>745023788500</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 반지형 웨어러블 디바이스 관련 기술력과 정부 지분 공시 등 긍정적 요인이 부각되며 급등 기대감이 형성됨. 주포 개입 가능성을 언급하며 강한 상승세를 예상함.</t>
+          <t>세계 최초 반지형 웨어러블 기기 관련 기술력 및 정부 지분 공시 기반 상승 기대. 주포의 적극적인 매수세 유입 및 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['웨어러블 디바이스', '정부 지분', '급등']</t>
+          <t>['웨어러블 기기', '정부 지분', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139200</v>
+        <v>140100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.82%</t>
+          <t>+14.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>146761411400</v>
+        <v>155096632150</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전 8기 수주 관련 260조 사업 규모의 구체적인 내용과 수익 계산법이 제시되며 긍정적인 전망이 우세함. 기관 및 연기금의 순매수세 유입도 긍정적 신호로 작용함.</t>
+          <t>미국 원전 8기 수주 및 260조 사업 구체화에 따른 상승 기대. AP1000 관련 사업성 분석 및 기관/연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '기관 연기금']</t>
+          <t>['원전 수주', '260조 사업', 'AP1000']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4070</v>
+        <v>20900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.69%</t>
+          <t>+13.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>205</v>
+        <v>786</v>
       </c>
       <c r="H6" t="n">
-        <v>1.56</v>
+        <v>10.47</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3580</v>
+        <v>18410</v>
       </c>
       <c r="K6" t="n">
-        <v>3600</v>
+        <v>18800</v>
       </c>
       <c r="L6" t="n">
-        <v>4335</v>
+        <v>20950</v>
       </c>
       <c r="M6" t="n">
-        <v>3450</v>
+        <v>18480</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>220133090515</v>
+        <v>338835453165</v>
       </c>
       <c r="P6" t="n">
-        <v>4335</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>1246</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-338000</v>
+        <v>256000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>207000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 건보료 적용 기대감으로 긍정적인 논조가 형성됨. 다만, 구체적인 실적 발표나 공시보다는 기대감에 기반한 언급이 주를 이룸.</t>
+          <t>원전 사업 및 미국 원전 건설 관련 신규 사업 재료 부각으로 인한 주가 상승 기대. 골든크로스 형성 및 시가총액 대비 저평가 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료 적용', '기대감']</t>
+          <t>['원전', '신사업', '건설']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20600</v>
+        <v>4000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.90%</t>
+          <t>+11.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>654</v>
+        <v>219</v>
       </c>
       <c r="H7" t="n">
-        <v>10.47</v>
+        <v>1.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18410</v>
+        <v>3580</v>
       </c>
       <c r="K7" t="n">
-        <v>18800</v>
+        <v>3600</v>
       </c>
       <c r="L7" t="n">
-        <v>20850</v>
+        <v>4335</v>
       </c>
       <c r="M7" t="n">
-        <v>18480</v>
+        <v>3450</v>
       </c>
       <c r="N7" t="n">
-        <v>10.4</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>311660409665</v>
+        <v>232807115237</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>256000</v>
+        <v>-338000</v>
       </c>
       <c r="S7" t="n">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 사업 수주 및 미국 원전 건설 관련 뉴스가 부각되며 주가 상승 기대감이 높음. 2만 돌파 및 시가총액 저평가 의견이 제시되며 긍정적인 전망을 보임.</t>
+          <t>탈모 치료제 관련 건보료 적용 시 큰 폭 상승 기대감. 10년 매집 및 차트상 긍정적 분석 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '신사업', '미국 건설']</t>
+          <t>['탈모 치료제', '건보료 적용', '10년 매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11990</v>
+        <v>12020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.80%</t>
+          <t>+10.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>264</v>
+        <v>320</v>
       </c>
       <c r="H8" t="n">
         <v>5.42</v>
@@ -1162,7 +1162,7 @@
         <v>5.53</v>
       </c>
       <c r="O8" t="n">
-        <v>101739671470</v>
+        <v>109461653960</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 체결 및 미국 원전 8기 수주 관련 뉴스가 주가 상승 모멘텀으로 작용하고 있음. 원전 섹터 전반의 강세와 함께 긍정적 전망을 보임.</t>
+          <t>원전 섹터 전반의 상승세 및 프랑스와의 원자력 협정 관련 호재. 대미 투자 원전 8기 관련 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원자력 협정', '미국 원전', '원전 섹터']</t>
+          <t>['원전', '프랑스 협력', '대미 투자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.02%</t>
+          <t>+6.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
         <v>5.34</v>
@@ -1254,7 +1254,7 @@
         <v>5.29</v>
       </c>
       <c r="O9" t="n">
-        <v>7191481676</v>
+        <v>7309908210</v>
       </c>
       <c r="P9" t="n">
         <v>901</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14150</v>
+        <v>50700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>425</v>
+        <v>184</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13470</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>13580</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>14450</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>13420</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>1.82</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>178608753115</v>
+        <v>103623558975</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-161000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'Texas', '투경']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50400</v>
+        <v>92500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.00%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>381</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="G11" t="n">
-        <v>188</v>
+        <v>1728</v>
       </c>
       <c r="H11" t="n">
-        <v>38.34</v>
+        <v>23.63</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>48000</v>
+        <v>87900</v>
       </c>
       <c r="K11" t="n">
-        <v>48550</v>
+        <v>91200</v>
       </c>
       <c r="L11" t="n">
-        <v>51600</v>
+        <v>93500</v>
       </c>
       <c r="M11" t="n">
-        <v>48350</v>
+        <v>90200</v>
       </c>
       <c r="N11" t="n">
-        <v>38.24</v>
+        <v>23.53</v>
       </c>
       <c r="O11" t="n">
-        <v>100309016575</v>
+        <v>319683913650</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>275000</v>
+        <v>-222000</v>
       </c>
       <c r="S11" t="n">
-        <v>66000</v>
+        <v>267000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['원전', 'SMR', '텍사스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92000</v>
+        <v>34225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.66%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>364</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>1701</v>
+        <v>255</v>
       </c>
       <c r="H12" t="n">
-        <v>23.63</v>
+        <v>52.69</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,152 +1515,152 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>87900</v>
+        <v>32750</v>
       </c>
       <c r="K12" t="n">
-        <v>91200</v>
+        <v>33700</v>
       </c>
       <c r="L12" t="n">
-        <v>93500</v>
+        <v>34350</v>
       </c>
       <c r="M12" t="n">
-        <v>90200</v>
+        <v>33450</v>
       </c>
       <c r="N12" t="n">
-        <v>23.53</v>
+        <v>21.02</v>
       </c>
       <c r="O12" t="n">
-        <v>301042717300</v>
+        <v>58057707600</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>69500</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>30400</v>
       </c>
       <c r="R12" t="n">
-        <v>-222000</v>
+        <v>324000</v>
       </c>
       <c r="S12" t="n">
-        <v>267000</v>
+        <v>194000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>텍사스 발전 사업 포함 원전 8기 수주 및 SMR 강자 이미지 부각. 트럼프 발표 소문 등 호재 다수.</t>
+          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '텍사스']</t>
+          <t>['원전', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34250</v>
+        <v>14070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>245</v>
+        <v>448</v>
       </c>
       <c r="H13" t="n">
-        <v>52.69</v>
+        <v>1.94</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>32750</v>
+        <v>13470</v>
       </c>
       <c r="K13" t="n">
-        <v>33700</v>
+        <v>13580</v>
       </c>
       <c r="L13" t="n">
-        <v>34350</v>
+        <v>14450</v>
       </c>
       <c r="M13" t="n">
-        <v>33450</v>
+        <v>13420</v>
       </c>
       <c r="N13" t="n">
-        <v>21.02</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>55203062750</v>
+        <v>184654490570</v>
       </c>
       <c r="P13" t="n">
-        <v>69500</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>30400</v>
+        <v>1252</v>
       </c>
       <c r="R13" t="n">
-        <v>324000</v>
+        <v>-161000</v>
       </c>
       <c r="S13" t="n">
-        <v>194000</v>
+        <v>11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>Texas 관련 소식 및 광통신 섹터 전반의 긍정적 분위기 속에서 주가 상승 기대감이 형성됨. 공매도 물량 언급과 함께 투경 재지정 여부가 주목받고 있음.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['광통신', 'Texas', '투경']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1850000</v>
+        <v>1859000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.76%</t>
+          <t>+4.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>2128</v>
+        <v>2114</v>
       </c>
       <c r="H14" t="n">
         <v>50.63</v>
@@ -1714,7 +1714,7 @@
         <v>50.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3041898609500</v>
+        <v>3280333620000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>낸드메모리 품귀 현상 및 반도체 시즌 2 도래 전망으로 주가 상승 기대감이 높음. 기관 및 외인 매수세 유입과 함께 300만 돌파 목표를 제시하는 등 긍정적 전망이 우세함.</t>
+          <t>반도체 품귀 현상 및 재고 감소 전망에 따른 200만 돌파 기대감. 자사주 매수 여력 및 한국 주식 시장 견인 역할 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['낸드메모리', '반도체', '기관 외인']</t>
+          <t>['반도체', '품귀 현상', '자사주 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15140</v>
+        <v>15100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" t="n">
         <v>1.72</v>
@@ -1806,7 +1806,7 @@
         <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>43952456650</v>
+        <v>44509141155</v>
       </c>
       <c r="P15" t="n">
         <v>21400</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>276750</v>
+        <v>277500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F16" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G16" t="n">
-        <v>1740</v>
+        <v>1774</v>
       </c>
       <c r="H16" t="n">
         <v>46.79</v>
@@ -1898,7 +1898,7 @@
         <v>46.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2240704915000</v>
+        <v>2456439327250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15조 규모 자사주 매수 및 주주환원 정책 발표로 긍정적 투자 심리가 형성됨. 30만 전자 목표 언급과 함께 개인 투자자들의 홀딩 의견이 지배적이나, 정치적 언급이 다소 혼재됨.</t>
+          <t>공매도 발악 및 숏커버링 기대감 속 28만 및 30만 돌파 전망. 자사주 매수 및 배당 확대 뉴스 기반 주주 환원 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주 매수', '주주환원', '반도체']</t>
+          <t>['공매도', '자사주 매수', '주주 환원']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8960</v>
+        <v>8930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H17" t="n">
         <v>1.68</v>
@@ -1990,7 +1990,7 @@
         <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>98256381975</v>
+        <v>101376099485</v>
       </c>
       <c r="P17" t="n">
         <v>25050</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10240</v>
+        <v>10230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.23</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
         <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H18" t="n">
         <v>0.44</v>
@@ -2082,7 +2082,7 @@
         <v>0.21</v>
       </c>
       <c r="O18" t="n">
-        <v>56786381370</v>
+        <v>58100332545</v>
       </c>
       <c r="P18" t="n">
         <v>20850</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15520</v>
+        <v>15460</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.66%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>29661605860</v>
+        <v>31258972165</v>
       </c>
       <c r="P19" t="n">
         <v>19380</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>건설주 강세 속 주가 부진. 대규모 투자 프로젝트 관련 언급 및 반등 기대.</t>
+          <t>호남 메가프로젝트 및 광주공항 재개장 관련 호재 가능성 언급. 반도체 조정 시 건설주 상승 추세에 따른 기대감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['건설', '투자', '반등']</t>
+          <t>['호남 메가프로젝트', '광주공항', '건설주']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11970</v>
+        <v>12040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.60%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
         <v>17.11</v>
@@ -2266,7 +2266,7 @@
         <v>18.05</v>
       </c>
       <c r="O20" t="n">
-        <v>24190282355</v>
+        <v>25405636355</v>
       </c>
       <c r="P20" t="n">
         <v>14350</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8340</v>
+        <v>8420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-11.84%</t>
+          <t>-10.99%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>24813441985</v>
+        <v>25620551935</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-93.14%</t>
+          <t>-92.98%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>769787659</v>
+        <v>826334598</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>
